--- a/test_data/gurindji_bush_tucker/data/metadata.xlsx
+++ b/test_data/gurindji_bush_tucker/data/metadata.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abby/Documents/Work/PosterWebsites/ro-crate-html-lite/test_data/gurindji_bush_tucker/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/uqfmeaki/Dropbox/2026_GurindjiBirds/Bush-foods/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2C21124-B218-0240-A80A-5D53D82DAE4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86AB6EB4-9290-9B40-A2A4-92EAE814729B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17280" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1280" yWindow="2120" windowWidth="30240" windowHeight="17260" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RootDataset" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="285">
   <si>
     <t>name</t>
   </si>
@@ -423,12 +423,6 @@
     <t>Bush Grain</t>
   </si>
   <si>
-    <t>They used to winnow seed in coolamons. The good part would fall down one way separated from the husks and the husks would spill over the other way. After that they would put the seed in another coolamon. They used to sprinkle water on it and then eat it.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kawarla-la na ngulu, manani warlmip-ma. Kilka waninyani ngu kuyapartak, purnku-ma. Nyawa waninyani jilipija-ma kuyapartak, jurlurl. Nyawa-nginyi-ma, ngulu yuwanani kawarla-la-ma. Ngawa-ngku ngulu kuya malykmalyk kunyjanani jaartkarra ngurnalu ngarnani. </t>
-  </si>
-  <si>
     <t>Many grasses</t>
   </si>
   <si>
@@ -483,9 +477,6 @@
 and mix it up. Native bee-hives or 'sugarbag' (in Kriol) contain sweet dark honey that is very tasty and much sought after. The hives also contain wax, pollen and eggs. The small bees have no sting and are harmless. Sugarbag is considered a mild laxative which 'opens up' your stomach. The general terms for sugarbag are 'namawurru' or 'ngarlu' which also refer to the sweet dark honey. The honey is referred to specifically as 'ngunyjung'. Sugarbag occurs in three main areas. One is found in hollows in trees, one occurs in the ground and the other in termite mounds. Ground sugarbag is called 'nangkalij' or 'nangkaliny' or 'yarlukura'. Tree sugarbag is called 'ngarlu' or 'namawurru'. The entrance hole of the hive is called 'jurrkiny' which has a nose or veranda over the hole. The small stingless bee is called 'nama' or 'lanu'. The yellow eggs and pollen in the hive are called 'kuntarri', 'kumpaying' or 'ngunyuwulij'. The wax is called 'jikala', 'piyarnak', or 'tarla'. The separation between the honey and wax, and the pollen is called 'jirnuk'. The honey, wax and pollen all mixed up together is referred to as 'kirrang'. A full hive is called 'ngitiwuny'. The egg of the bee is called 'kurla'. Bee droppings are called 'jayurrk' and are seen below the hive entrance holes on the ground. This signals that the hive is active. The word for sugarbag season is 'tulwarrangkarrakmirntij' (the season of blossoms) and there are specific words for chopping at a tree to get honey, 'pirntirrp' or 'tarlawurlp' and digging into the hole with your fingers and sampling the honey, 'ngampij' or 'ngapinykarra'. A stick or small brush which is used to get honey out of a tree that cannot be chopped open is called a 'jamawurn'.</t>
   </si>
   <si>
-    <t>Karrajkarraj-ma. Nyila na ngulu-rla manani marlin-ma. Kurrku ngulu-rla kuya na kurrku pirrkap manani. Yuwani ngulu murlangka-ma. Ngulu-rla wumara yuwanani kuruwarrany yapayapa. Jakarr ngulu manani yalangku marlin-tu-ma. Yalanginyi-ma pakarli-lu na jakarr kankulupal-a-nginyi-ma. Nyamu jiyarnani kalypak-ma ngulu ngarnani jaartkarra na.</t>
-  </si>
-  <si>
     <t>Namawurru-ma. Kurru ngulu nyangani kuyangku, ngulu nyangani kankula karrap nama-walija. Paraj ngulu pungani karnti-ka. Tikap na ngulu panani namawurru-ma nyila-ma. Ngulu manani kumpaying purrupurru ngarlu ngulu manani. Yuwanani ngulu parlak.</t>
   </si>
   <si>
@@ -565,9 +556,6 @@
     <t>files/images/IMG_0279.jpg</t>
   </si>
   <si>
-    <t>Nicole Zicchino</t>
-  </si>
-  <si>
     <t>Glenn Wightman</t>
   </si>
   <si>
@@ -589,18 +577,12 @@
     <t>files/audio/sentences/13_Kurlartarti_VW.mp3</t>
   </si>
   <si>
-    <t>files/audio/sentences/06_Mintaarraj_VWw.mp3</t>
-  </si>
-  <si>
     <t>files/audio/sentences/04_Wayita_VW.mp3</t>
   </si>
   <si>
     <t>files/audio/sentences/07_Kinyjirrka_VW.mp3</t>
   </si>
   <si>
-    <t>files/audio/names/01_Muying_VW.mp3</t>
-  </si>
-  <si>
     <t>files/audio/sentences/11_Kurtakarla_VW.mp3</t>
   </si>
   <si>
@@ -628,9 +610,6 @@
     <t>files/audio/names/ngamanpurru_VW.mp3</t>
   </si>
   <si>
-    <t>files/audio/names/ngarlu_SO.mp3</t>
-  </si>
-  <si>
     <t>files/audio/names/kurlartarti_VW.mp3</t>
   </si>
   <si>
@@ -649,12 +628,6 @@
     <t>files/audio/names/kurtakarla_VW1.mp3</t>
   </si>
   <si>
-    <t>files/audio/sentences/kaaril_VW.mp3</t>
-  </si>
-  <si>
-    <t>files/audio/names/partiki_VW.mp3.mp3</t>
-  </si>
-  <si>
     <t>files/audio/names/kunanturu_VW.mp3</t>
   </si>
   <si>
@@ -685,9 +658,6 @@
     <t>files/audio/sentences/wiyinti_BW_eg1_Ngurnalu.mp3</t>
   </si>
   <si>
-    <t>files/audio/sentences/martiya_VW_eg2_Ngulu.mp3</t>
-  </si>
-  <si>
     <t>files/audio/sentences/purnku_VW_eg1_Kawarla.mp3</t>
   </si>
   <si>
@@ -914,6 +884,39 @@
   </si>
   <si>
     <t>files/images/Yangunungku_02.jpg</t>
+  </si>
+  <si>
+    <t>files/audio/names/kaaril_VW.mp3</t>
+  </si>
+  <si>
+    <t>Karrajkarraj-ma. Nyila na ngulu-rla manani marlin-ma. Kurrku ngulu-rla kuya na kurrku pirrkap manani. Yuwanani ngulu murlangka-ma. Ngulu-rla wumara yuwanani kuruwarrany yapayapa. Jakarr ngulu manani yalangku marlin-tu-ma. Yalanginyi-ma pakarli-lu na jakarr kankulupal-a-nginyi-ma. Nyamu jiyarnani kalypak-ma ngulu ngarnani jaartkarra na.</t>
+  </si>
+  <si>
+    <t>files/audio/sentences/kamara_VW.mp3</t>
+  </si>
+  <si>
+    <t>files/audio/sentences/martiya_VW.mp3</t>
+  </si>
+  <si>
+    <t>files/audio/sentences/01_Muying_VW.mp3</t>
+  </si>
+  <si>
+    <t>files/audio/names/ngarlu_AC.mp3</t>
+  </si>
+  <si>
+    <t>Kawarla-la na ngulu, manani warlmip-ma kawarla-la-ma, warlmip. Kilka waninyani ngu kuyapartak, purnku na. Nyawa waninyani jilipija-ma kuyapartak, jurlurl. Nyawa-nginyi-ma, ngulu yuwanani kawarla-la-ma ngurnalu, nguyinangulu, jayingani na ngurnalu yuwanani nyila-ma kilka-ma. Ngawa-ngku ngulu kuya malykmalyk kunyjanani jaartkarra ngurnalu ngarnani. Nyila-ma, pirlkiya-ma nyawa-ma waninyani kuyapartak-ma jurlurl-ma. Nyila-ma purnku-ma. Jilipija-ma, nyila-ma ngulu manani kuya gigin. Ngulu yuwanani. Ngawa-yawung-kulu ngurnalu luwanani jaartkarra. Jangkakarni-lu yapayapa-lu. Laik nyamu-rnalu karrinyani tanku-murlung-kula yu nou, ngantipa.</t>
+  </si>
+  <si>
+    <t>They used to winnow (seed) in a coolamon. The good part would fall down one way clean (separated from the husks). And the husks would spill over the other way. After that they would put it in another coolamon. They showed us so we know how to put the seed in the coolamon. They used to sprinkle water on it and then eat it. It's the white one that spills out this way. That's the good grain. And it was the husks that they would separate from it. Then they'd put it [in a coolamon]. We'd eat it mixed with water. Adults and kids alike. Like during the times we had no food.</t>
+  </si>
+  <si>
+    <t>files/audio/names/partiki_VW.mp3</t>
+  </si>
+  <si>
+    <t>files/audio/sentences/Walarri_VW.mp3</t>
+  </si>
+  <si>
+    <t>Nicole Zicchino showing Rosemary Johnson cooking damper</t>
   </si>
 </sst>
 </file>
@@ -1391,7 +1394,7 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -1399,7 +1402,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -1487,7 +1490,7 @@
         <v>13</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>14</v>
@@ -1505,7 +1508,7 @@
         <v>18</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="M1" s="2" t="s">
         <v>19</v>
@@ -1520,10 +1523,10 @@
         <v>22</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="160" x14ac:dyDescent="0.2">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" ht="176" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="str">
         <f t="shared" ref="A2:A18" si="0">_xlfn.CONCAT("#", C2)</f>
         <v>#karrajkarraj</v>
@@ -1550,10 +1553,10 @@
         <v>70</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>140</v>
+        <v>275</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>67</v>
@@ -1562,13 +1565,13 @@
         <v>69</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="240" x14ac:dyDescent="0.2">
@@ -1601,25 +1604,25 @@
         <v>72</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>73</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="Q3" s="7"/>
     </row>
@@ -1650,10 +1653,10 @@
         <v>76</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>75</v>
@@ -1662,13 +1665,13 @@
         <v>74</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="409.6" x14ac:dyDescent="0.2">
@@ -1701,28 +1704,28 @@
         <v>80</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>82</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>188</v>
+        <v>279</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="Q5" s="7" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="64" x14ac:dyDescent="0.2">
@@ -1752,10 +1755,10 @@
         <v>84</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="L6" s="3" t="s">
         <v>75</v>
@@ -1764,13 +1767,13 @@
         <v>83</v>
       </c>
       <c r="N6" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="192" x14ac:dyDescent="0.2">
@@ -1800,10 +1803,10 @@
         <v>87</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="L7" s="3" t="s">
         <v>67</v>
@@ -1812,13 +1815,13 @@
         <v>88</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="48" x14ac:dyDescent="0.2">
@@ -1848,25 +1851,25 @@
         <v>91</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>89</v>
       </c>
       <c r="N8" s="3" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="224" x14ac:dyDescent="0.2">
@@ -1896,10 +1899,10 @@
         <v>93</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>67</v>
@@ -1908,13 +1911,13 @@
         <v>94</v>
       </c>
       <c r="N9" s="3" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="P9" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="208" x14ac:dyDescent="0.2">
@@ -1944,25 +1947,25 @@
         <v>96</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>95</v>
       </c>
       <c r="N10" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>178</v>
+        <v>278</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="64" x14ac:dyDescent="0.2">
@@ -1992,10 +1995,10 @@
         <v>99</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="L11" s="3" t="s">
         <v>75</v>
@@ -2004,13 +2007,13 @@
         <v>100</v>
       </c>
       <c r="N11" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="192" x14ac:dyDescent="0.2">
@@ -2043,10 +2046,10 @@
         <v>102</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>67</v>
@@ -2055,13 +2058,13 @@
         <v>101</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>195</v>
+        <v>274</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="112" x14ac:dyDescent="0.2">
@@ -2091,10 +2094,10 @@
         <v>106</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="L13" s="3" t="s">
         <v>67</v>
@@ -2103,13 +2106,13 @@
         <v>107</v>
       </c>
       <c r="N13" s="3" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>196</v>
+        <v>282</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="80" x14ac:dyDescent="0.2">
@@ -2139,10 +2142,10 @@
         <v>109</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>67</v>
@@ -2151,13 +2154,13 @@
         <v>108</v>
       </c>
       <c r="N14" s="3" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="112" x14ac:dyDescent="0.2">
@@ -2187,10 +2190,10 @@
         <v>112</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>67</v>
@@ -2199,16 +2202,16 @@
         <v>62</v>
       </c>
       <c r="N15" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q15" s="7" t="s">
         <v>230</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="Q15" s="7" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="144" x14ac:dyDescent="0.2">
@@ -2247,22 +2250,25 @@
         <v>115</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>116</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>199</v>
+        <v>190</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>276</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" ht="128" x14ac:dyDescent="0.2">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="304" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="str">
         <f t="shared" si="0"/>
         <v>#ngurlu</v>
@@ -2289,25 +2295,25 @@
         <v>120</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>122</v>
+        <v>280</v>
       </c>
       <c r="K17" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="M17" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>123</v>
-      </c>
       <c r="N17" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="128" x14ac:dyDescent="0.2">
@@ -2319,7 +2325,7 @@
         <v>23</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>3</v>
@@ -2334,28 +2340,28 @@
         <v>25</v>
       </c>
       <c r="I18" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>127</v>
-      </c>
       <c r="K18" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="M18" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="N18" s="3" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>207</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19" spans="1:17" ht="144" x14ac:dyDescent="0.2">
@@ -2367,7 +2373,7 @@
         <v>23</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>3</v>
@@ -2382,28 +2388,28 @@
         <v>25</v>
       </c>
       <c r="I19" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="K19" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>132</v>
       </c>
       <c r="L19" s="3" t="s">
         <v>81</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
     </row>
     <row r="20" spans="1:17" ht="144" x14ac:dyDescent="0.2">
@@ -2415,7 +2421,7 @@
         <v>23</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>3</v>
@@ -2430,28 +2436,31 @@
         <v>25</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="N20" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>203</v>
+        <v>194</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>283</v>
       </c>
       <c r="Q20" s="7" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="128" x14ac:dyDescent="0.2">
@@ -2463,7 +2472,7 @@
         <v>23</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>3</v>
@@ -2478,31 +2487,31 @@
         <v>25</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>67</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="N21" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="P21" s="3" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="Q21" s="7" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="224" x14ac:dyDescent="0.2">
@@ -2514,7 +2523,7 @@
         <v>23</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>3</v>
@@ -2529,22 +2538,22 @@
         <v>25</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="K22" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="M22" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="N22" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -2562,7 +2571,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D147"/>
+  <dimension ref="A1:D149"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="69" customWidth="1"/>
@@ -2583,693 +2592,707 @@
     </row>
     <row r="2" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="B2" t="s">
         <v>27</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="B3" t="s">
         <v>27</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="B5" t="s">
         <v>27</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B10" t="s">
         <v>27</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>236</v>
-      </c>
-      <c r="B11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>188</v>
+        <v>279</v>
       </c>
       <c r="B12" t="s">
         <v>27</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B13" t="s">
         <v>27</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B14" t="s">
         <v>27</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="B15" t="s">
         <v>27</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B16" t="s">
         <v>27</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="B17" t="s">
         <v>27</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="B18" t="s">
         <v>27</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>175</v>
+        <v>254</v>
       </c>
       <c r="B19" t="s">
         <v>27</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="B20" t="s">
         <v>27</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="B21" t="s">
         <v>27</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B22" t="s">
         <v>27</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="B23" t="s">
         <v>27</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="B24" t="s">
         <v>27</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B25" t="s">
         <v>27</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B26" t="s">
         <v>27</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="B27" t="s">
         <v>27</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>178</v>
+        <v>278</v>
       </c>
       <c r="B28" t="s">
         <v>27</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B29" t="s">
         <v>27</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="B30" t="s">
         <v>27</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="B31" t="s">
         <v>27</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="B32" t="s">
         <v>27</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>195</v>
+        <v>274</v>
       </c>
       <c r="B33" t="s">
         <v>27</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="B34" t="s">
         <v>27</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="B35" t="s">
         <v>27</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>196</v>
+        <v>282</v>
       </c>
       <c r="B36" t="s">
         <v>27</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="B37" t="s">
         <v>27</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="B38" t="s">
         <v>27</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="B39" t="s">
         <v>27</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="B40" t="s">
         <v>27</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B41" t="s">
         <v>27</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="B42" t="s">
         <v>27</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="B43" t="s">
         <v>27</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B44" t="s">
         <v>27</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="B45" t="s">
         <v>27</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
-        <v>166</v>
+        <v>276</v>
       </c>
       <c r="B46" t="s">
         <v>27</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
-        <v>200</v>
+        <v>163</v>
       </c>
       <c r="B47" t="s">
         <v>27</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="B48" t="s">
         <v>27</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
     </row>
     <row r="49" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
-        <v>282</v>
+        <v>198</v>
       </c>
       <c r="B49" t="s">
         <v>27</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
     </row>
     <row r="50" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>201</v>
+        <v>272</v>
       </c>
       <c r="B50" t="s">
         <v>27</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
     </row>
     <row r="51" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="B51" t="s">
         <v>27</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
     </row>
     <row r="52" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
-        <v>169</v>
+        <v>277</v>
       </c>
       <c r="B52" t="s">
         <v>27</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
     </row>
     <row r="53" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
-        <v>202</v>
+        <v>165</v>
       </c>
       <c r="B53" t="s">
         <v>27</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="54" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="3" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="B54" t="s">
         <v>27</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="55" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="3" t="s">
-        <v>164</v>
+        <v>197</v>
       </c>
       <c r="B55" t="s">
         <v>27</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="3" t="s">
-        <v>203</v>
+        <v>161</v>
       </c>
       <c r="B56" t="s">
         <v>27</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="3" t="s">
-        <v>152</v>
+        <v>194</v>
       </c>
       <c r="B57" t="s">
         <v>27</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
     </row>
     <row r="58" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
-        <v>204</v>
+        <v>283</v>
       </c>
       <c r="B58" t="s">
         <v>27</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
     </row>
     <row r="59" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="3" t="s">
-        <v>184</v>
+        <v>149</v>
       </c>
       <c r="B59" t="s">
         <v>27</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>160</v>
+        <v>195</v>
       </c>
       <c r="B60" t="s">
         <v>27</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>205</v>
+        <v>178</v>
       </c>
       <c r="B61" t="s">
         <v>27</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>277</v>
+        <v>252</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A62" s="3" t="s">
+        <v>157</v>
       </c>
       <c r="B62" t="s">
         <v>27</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A63" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B63" t="s">
+        <v>27</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>267</v>
+      </c>
+      <c r="B64" t="s">
+        <v>27</v>
+      </c>
+      <c r="C64" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>278</v>
-      </c>
-      <c r="B63" t="s">
-        <v>27</v>
-      </c>
-      <c r="C63" t="s">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>268</v>
+      </c>
+      <c r="B65" t="s">
+        <v>27</v>
+      </c>
+      <c r="C65" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A64" s="3"/>
-      <c r="C64" s="3"/>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A65" s="3"/>
-      <c r="C65" s="3"/>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A66" s="3"/>
@@ -3598,6 +3621,14 @@
     <row r="147" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A147" s="3"/>
       <c r="C147" s="3"/>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A148" s="3"/>
+      <c r="C148" s="3"/>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A149" s="3"/>
+      <c r="C149" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3642,10 +3673,10 @@
         <v>63</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -3659,10 +3690,10 @@
         <v>66</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -3812,7 +3843,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
@@ -3821,35 +3852,35 @@
         <v>58</v>
       </c>
       <c r="D10" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="D11" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="B12" t="s">
         <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="D12" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
     </row>
   </sheetData>
